--- a/relatorios/Mogo/Movimentacao Credito Cliente/03-2026.xlsx
+++ b/relatorios/Mogo/Movimentacao Credito Cliente/03-2026.xlsx
@@ -57,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,15 +501,11 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>224,00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="D2" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -543,15 +540,11 @@
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>224,00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>224,00</t>
-        </is>
+      <c r="D3" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>224</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -590,15 +583,11 @@
           <t>07405701701</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.880,00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2.880,00</t>
-        </is>
+      <c r="D4" s="2" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -637,15 +626,11 @@
           <t>54944066600</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>237,00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="D5" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -684,15 +669,11 @@
           <t>54944066600</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>237,00</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>237,00</t>
-        </is>
+      <c r="D6" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>237</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -731,15 +712,11 @@
           <t>07836630722</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>36,85</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>300,61</t>
-        </is>
+      <c r="D7" s="2" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>300.61</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -778,15 +755,11 @@
           <t>07836630722</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>36,85</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>337,46</t>
-        </is>
+      <c r="D8" s="2" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>337.46</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -825,15 +798,11 @@
           <t>02045628728</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>21,80</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="D9" s="2" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -872,15 +841,11 @@
           <t>66723388704</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="D10" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -919,15 +884,11 @@
           <t>02163156702</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>330,00</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="D11" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -966,15 +927,11 @@
           <t>02163156702</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>330,00</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>330,00</t>
-        </is>
+      <c r="D12" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>330</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1013,15 +970,11 @@
           <t>07386953780</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
+      <c r="D13" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>74</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1060,15 +1013,11 @@
           <t>66723388704</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
+      <c r="D14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>100</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1099,15 +1048,11 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="D15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1142,15 +1087,11 @@
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="D16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1185,15 +1126,11 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>211,00</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+      <c r="D17" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1228,15 +1165,11 @@
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>215,00</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>215,00</t>
-        </is>
+      <c r="D18" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
